--- a/data/trans_dic/P05A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P05A_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,46; 36,32</t>
+          <t>27,85; 36,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,65; 49,52</t>
+          <t>40,33; 50,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,1; 43,98</t>
+          <t>33,69; 43,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,71; 27,84</t>
+          <t>19,51; 27,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,82; 38,73</t>
+          <t>28,52; 38,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,49; 49,17</t>
+          <t>36,93; 48,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,5; 46,27</t>
+          <t>36,16; 46,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,67; 27,79</t>
+          <t>21,17; 28,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 35,95</t>
+          <t>29,02; 35,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,68; 48,0</t>
+          <t>40,37; 48,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,17; 43,55</t>
+          <t>35,98; 43,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,14; 27,1</t>
+          <t>21,32; 26,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,47; 36,76</t>
+          <t>26,69; 36,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 45,47</t>
+          <t>34,9; 45,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,68; 41,78</t>
+          <t>31,76; 41,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,93; 21,22</t>
+          <t>14,12; 21,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,64; 34,66</t>
+          <t>25,31; 34,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,36; 47,52</t>
+          <t>36,61; 47,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,27; 43,71</t>
+          <t>33,75; 43,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 29,21</t>
+          <t>20,83; 28,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,32; 34,29</t>
+          <t>27,35; 34,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 44,59</t>
+          <t>36,96; 44,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,33; 41,5</t>
+          <t>34,29; 41,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,35; 23,66</t>
+          <t>18,15; 23,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,75; 33,75</t>
+          <t>25,34; 33,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,54; 45,17</t>
+          <t>37,29; 45,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,89; 40,64</t>
+          <t>31,93; 40,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 23,03</t>
+          <t>17,38; 25,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,38; 45,08</t>
+          <t>30,37; 44,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,18; 46,1</t>
+          <t>33,97; 46,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,17; 43,55</t>
+          <t>28,0; 43,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,08; 25,15</t>
+          <t>15,55; 25,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,91; 35,1</t>
+          <t>28,36; 35,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,43; 44,06</t>
+          <t>37,66; 44,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,42; 39,7</t>
+          <t>31,93; 39,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 22,31</t>
+          <t>17,71; 24,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,29; 31,68</t>
+          <t>26,67; 32,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,32; 43,26</t>
+          <t>37,05; 43,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,09; 38,73</t>
+          <t>33,27; 38,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 18,98</t>
+          <t>14,01; 18,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,85; 38,9</t>
+          <t>32,06; 38,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 43,45</t>
+          <t>36,38; 43,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,83; 40,73</t>
+          <t>34,03; 40,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 61,83</t>
+          <t>18,51; 23,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,39; 33,37</t>
+          <t>29,17; 33,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,49; 42,14</t>
+          <t>37,72; 42,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 38,6</t>
+          <t>34,14; 38,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 52,06</t>
+          <t>16,62; 20,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,08; 37,09</t>
+          <t>26,85; 37,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,87; 38,38</t>
+          <t>30,01; 38,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,12; 38,58</t>
+          <t>30,74; 38,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 22,25</t>
+          <t>15,33; 22,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,25; 42,86</t>
+          <t>34,38; 42,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,63; 39,93</t>
+          <t>32,82; 39,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,19; 40,14</t>
+          <t>33,17; 40,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,43; 19,43</t>
+          <t>17,85; 22,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,63; 39,25</t>
+          <t>32,75; 39,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,77; 38,44</t>
+          <t>32,71; 38,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,01; 38,49</t>
+          <t>32,94; 38,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,13; 19,51</t>
+          <t>17,51; 21,5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,93; 29,01</t>
+          <t>18,39; 28,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,57; 41,91</t>
+          <t>30,22; 42,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,85; 40,2</t>
+          <t>29,12; 40,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 26,46</t>
+          <t>10,3; 26,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,59; 35,65</t>
+          <t>30,53; 35,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,95; 43,76</t>
+          <t>38,33; 44,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,56; 37,75</t>
+          <t>31,71; 37,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,06; 16,99</t>
+          <t>12,39; 17,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,83; 33,45</t>
+          <t>28,97; 33,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,42; 43,15</t>
+          <t>37,3; 42,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,05; 37,38</t>
+          <t>31,74; 37,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 17,71</t>
+          <t>12,72; 18,05</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,95; 31,18</t>
+          <t>27,84; 31,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,17; 41,66</t>
+          <t>38,13; 41,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,26; 37,52</t>
+          <t>34,27; 37,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 19,16</t>
+          <t>17,11; 20,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,76; 36,05</t>
+          <t>32,8; 35,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,23; 41,65</t>
+          <t>38,26; 41,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,08; 38,4</t>
+          <t>34,99; 38,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,58; 36,19</t>
+          <t>18,85; 21,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,89; 33,2</t>
+          <t>30,88; 33,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,66; 41,09</t>
+          <t>38,48; 41,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35,03; 37,52</t>
+          <t>35,01; 37,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,38; 28,22</t>
+          <t>18,44; 20,39</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118747</t>
+          <t>127513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>107095</t>
+          <t>118930</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>225843</t>
+          <t>246443</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>130104; 172098</t>
+          <t>131958; 170858</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>173359; 216521</t>
+          <t>176335; 219390</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146310; 188720</t>
+          <t>144573; 186751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99578; 140666</t>
+          <t>107428; 150346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>85332; 118762</t>
+          <t>87470; 118210</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>117875; 154608</t>
+          <t>116117; 152997</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>123190; 160585</t>
+          <t>125489; 162002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92209; 123968</t>
+          <t>103103; 137190</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>227581; 280539</t>
+          <t>226518; 280477</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>305778; 360806</t>
+          <t>303425; 360850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>280734; 338029</t>
+          <t>279290; 337713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>201066; 257769</t>
+          <t>221215; 279621</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>82031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95217</t>
+          <t>103463</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>172839</t>
+          <t>185495</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97137; 134895</t>
+          <t>97927; 134220</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146844; 190413</t>
+          <t>146153; 190323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119521; 157596</t>
+          <t>119815; 157023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62994; 95952</t>
+          <t>68232; 102840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95347; 128890</t>
+          <t>94104; 128699</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122278; 159813</t>
+          <t>123131; 160305</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>123838; 162716</t>
+          <t>125636; 162815</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81742; 111754</t>
+          <t>88127; 118811</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201812; 253306</t>
+          <t>202087; 254456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>281022; 336698</t>
+          <t>279076; 339010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>257321; 311007</t>
+          <t>256971; 309144</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153185; 197535</t>
+          <t>164516; 212145</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91670</t>
+          <t>99173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>125316</t>
+          <t>137158</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>139692; 183059</t>
+          <t>137445; 181783</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>235721; 283597</t>
+          <t>234152; 284966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166420; 212087</t>
+          <t>166634; 210240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32848; 153886</t>
+          <t>81976; 120208</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50966; 75638</t>
+          <t>50959; 75192</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88555; 119462</t>
+          <t>88026; 121482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46791; 72351</t>
+          <t>46510; 72577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25169; 41981</t>
+          <t>29152; 47345</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>198215; 249258</t>
+          <t>201432; 248621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>332039; 390772</t>
+          <t>334009; 395459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>223063; 273178</t>
+          <t>219665; 273904</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58824; 186312</t>
+          <t>116706; 159746</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164749</t>
+          <t>181880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>361621</t>
+          <t>181092</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>526370</t>
+          <t>362972</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>325565; 392320</t>
+          <t>330318; 396819</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>431098; 499740</t>
+          <t>427943; 498044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>380383; 445286</t>
+          <t>382452; 446601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138789; 196381</t>
+          <t>158467; 213106</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>227473; 277832</t>
+          <t>228992; 278255</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>276407; 332690</t>
+          <t>278557; 334633</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>279366; 336391</t>
+          <t>281084; 335703</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>188272; 604770</t>
+          <t>159411; 202031</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>573926; 651618</t>
+          <t>569646; 651897</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>720047; 809479</t>
+          <t>724541; 814342</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>673206; 762608</t>
+          <t>674504; 761418</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>346774; 1047761</t>
+          <t>330966; 400517</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86197</t>
+          <t>105435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>139056</t>
+          <t>166545</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>225252</t>
+          <t>271981</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94915; 130036</t>
+          <t>94135; 130440</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152512; 195952</t>
+          <t>153238; 196231</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193135; 239471</t>
+          <t>190822; 239644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69463; 105696</t>
+          <t>87066; 125577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>194803; 243792</t>
+          <t>195547; 242477</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>248196; 303675</t>
+          <t>249649; 301711</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>244699; 295933</t>
+          <t>244512; 295452</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>104541; 163445</t>
+          <t>148303; 187033</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>299985; 360822</t>
+          <t>301029; 360781</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>416530; 488576</t>
+          <t>415766; 483349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>448286; 522688</t>
+          <t>447337; 519852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>186011; 256873</t>
+          <t>244941; 300716</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>122211</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>149306</t>
+          <t>163693</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56435; 86507</t>
+          <t>54848; 83930</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>81576; 111857</t>
+          <t>80659; 112251</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82473; 114935</t>
+          <t>83260; 115756</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22508; 63639</t>
+          <t>24438; 63828</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>382050; 445234</t>
+          <t>381270; 447111</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>420589; 485025</t>
+          <t>424776; 490610</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>341066; 407932</t>
+          <t>342662; 406954</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91804; 129333</t>
+          <t>104575; 144379</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>445958; 517398</t>
+          <t>448083; 519853</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>514522; 593314</t>
+          <t>512901; 589461</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>438072; 510846</t>
+          <t>433781; 507469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>123043; 177402</t>
+          <t>137598; 195203</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>578924</t>
+          <t>637515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>846002</t>
+          <t>730227</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1424925</t>
+          <t>1367742</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>914017; 1019596</t>
+          <t>910438; 1018503</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1303956; 1423479</t>
+          <t>1302571; 1420676</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1159535; 1269790</t>
+          <t>1159693; 1274501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>444486; 646860</t>
+          <t>588895; 695007</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1106510; 1217764</t>
+          <t>1108080; 1215029</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1354929; 1476207</t>
+          <t>1355963; 1475550</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1238121; 1355221</t>
+          <t>1234924; 1354000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>664562; 1294259</t>
+          <t>684886; 776359</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2053585; 2206947</t>
+          <t>2053073; 2199471</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2690695; 2860182</t>
+          <t>2678523; 2855471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2422132; 2594163</t>
+          <t>2420761; 2585558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1208312; 1961601</t>
+          <t>1304909; 1442309</t>
         </is>
       </c>
     </row>
